--- a/Configs/GameConfig/Datas/Board.xlsx
+++ b/Configs/GameConfig/Datas/Board.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board" sheetId="1" r:id="R1b07625f89464fef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board" sheetId="1" r:id="Rdfb6add4ec1f470b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -605,10 +605,8 @@
       <x:c r="B5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BilliardsTable</x:t>
-        </x:is>
+      <x:c r="C5" t="str">
+        <x:v>Table</x:v>
       </x:c>
       <x:c r="D5" t="inlineStr">
         <x:is>
